--- a/Frankrig_2026_opdelt_per_hold.xlsx
+++ b/Frankrig_2026_opdelt_per_hold.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sofushansen/HelloWorld/Karting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5D8419-D8F1-7D4C-97CF-87D1261AD6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66037483-937A-3644-AE61-FBF99B0CB26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14900" yWindow="760" windowWidth="19660" windowHeight="21580" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,10 +591,10 @@
     <t>Sofus 7</t>
   </si>
   <si>
-    <t>Madsen 9</t>
+    <t>Sofus 8</t>
   </si>
   <si>
-    <t>Sofus 8</t>
+    <t>Sofus 9</t>
   </si>
 </sst>
 </file>
